--- a/Sales_Data_Analysis.xlsx
+++ b/Sales_Data_Analysis.xlsx
@@ -17,6 +17,9 @@
     <sheet name="Sheet2" sheetId="6" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlchart.0" hidden="1">Sheet2!$D$4:$D$7</definedName>
+    <definedName name="_xlchart.1" hidden="1">Sheet2!$E$3</definedName>
+    <definedName name="_xlchart.2" hidden="1">Sheet2!$E$4:$E$7</definedName>
     <definedName name="A">Sheet1!$I$11</definedName>
     <definedName name="sales_data" localSheetId="1">Sheet1!$A$1:$G$22</definedName>
   </definedNames>
@@ -51,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="33">
   <si>
     <t>OrderID</t>
   </si>
@@ -151,15 +154,12 @@
   <si>
     <t>Metric</t>
   </si>
-  <si>
-    <t>Regional Sales Analysis</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -186,14 +186,6 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -241,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -278,7 +270,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -315,7 +306,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Sales_Data_Analysis.xlsx]Sheet5!PivotTable4</c:name>
+    <c:name>[Regional Sales Analysis.xlsx]Sheet5!PivotTable4</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -709,6 +700,32 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Regional Sales Analysis</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
@@ -723,11 +740,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -741,15 +758,20 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:view3D>
-      <c:rotX val="15"/>
-      <c:rotY val="20"/>
-      <c:depthPercent val="100"/>
-      <c:rAngAx val="1"/>
+      <c:rotX val="0"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="60"/>
+      <c:rAngAx val="0"/>
+      <c:perspective val="100"/>
     </c:view3D>
     <c:floor>
       <c:thickness val="0"/>
       <c:spPr>
-        <a:noFill/>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -793,36 +815,109 @@
               <c:f>Sheet2!$E$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sales</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="accent1">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
             </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
-            <a:sp3d/>
+            <a:sp3d contourW="9525">
+              <a:contourClr>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:contourClr>
+            </a:sp3d>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="50000"/>
+                          <a:lumOff val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Sheet2!$D$4:$D$7</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>Region</c:v>
+                  <c:v>West</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>West</c:v>
+                  <c:v>North</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>North</c:v>
+                  <c:v>East</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>East</c:v>
+                  <c:v>South</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -834,42 +929,42 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>34600</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>34600</c:v>
+                  <c:v>32650</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>32650</c:v>
+                  <c:v>17500</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>17500</c:v>
+                  <c:v>17400</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-33F6-468A-8128-4EE1A347B262}"/>
+              <c16:uniqueId val="{00000000-D219-4EA8-BE8C-D83B530229EB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
+        <c:gapWidth val="65"/>
         <c:shape val="box"/>
-        <c:axId val="799530975"/>
-        <c:axId val="799538463"/>
+        <c:axId val="684029471"/>
+        <c:axId val="684037791"/>
         <c:axId val="0"/>
       </c:bar3DChart>
       <c:catAx>
-        <c:axId val="799530975"/>
+        <c:axId val="684029471"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -881,8 +976,14 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln>
-            <a:noFill/>
+          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -891,11 +992,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -906,7 +1007,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="799538463"/>
+        <c:crossAx val="684037791"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -914,7 +1015,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="799538463"/>
+        <c:axId val="684037791"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -924,7 +1025,7 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
+                <a:schemeClr val="dk1">
                   <a:lumMod val="15000"/>
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
@@ -952,9 +1053,9 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -965,7 +1066,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="799530975"/>
+        <c:crossAx val="684029471"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -982,14 +1083,30 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="39000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:round/>
@@ -1598,160 +1715,216 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="288">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
+      <a:schemeClr val="dk1">
         <a:lumMod val="75000"/>
         <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="dk1">
             <a:lumMod val="25000"/>
             <a:lumOff val="75000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
       <a:spAutoFit/>
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -1767,16 +1940,112 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:sp3d/>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -1784,158 +2053,60 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
             <a:lumMod val="50000"/>
             <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -1944,27 +2115,35 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -1972,11 +2151,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr/>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -1984,14 +2164,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2003,12 +2183,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -2017,14 +2197,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -2033,9 +2212,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2045,20 +2224,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -2067,11 +2245,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -2079,14 +2262,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -2130,20 +2307,20 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>19051</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>133351</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="7" name="Chart 6"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -3391,28 +3568,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>25</v>
       </c>
       <c r="B1" s="7"/>
     </row>
-    <row r="2" spans="1:9" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
-      <c r="I2" s="16" t="s">
-        <v>33</v>
-      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>32</v>
       </c>
@@ -3420,8 +3593,14 @@
         <v>26</v>
       </c>
       <c r="C3" s="6"/>
+      <c r="D3" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>27</v>
       </c>
@@ -3429,14 +3608,14 @@
         <v>20</v>
       </c>
       <c r="C4" s="6"/>
-      <c r="D4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
+      <c r="D4" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4">
+        <v>34600</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>28</v>
       </c>
@@ -3444,14 +3623,14 @@
         <v>102150</v>
       </c>
       <c r="C5" s="6"/>
-      <c r="D5" t="s">
-        <v>7</v>
+      <c r="D5" s="15" t="s">
+        <v>10</v>
       </c>
       <c r="E5">
-        <v>34600</v>
+        <v>32650</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>29</v>
       </c>
@@ -3459,14 +3638,14 @@
         <v>5107.5</v>
       </c>
       <c r="C6" s="6"/>
-      <c r="D6" t="s">
-        <v>10</v>
+      <c r="D6" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>32650</v>
+        <v>17500</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>30</v>
       </c>
@@ -3475,24 +3654,18 @@
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E7">
-        <v>17500</v>
+        <v>17400</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B8" s="14">
         <v>400</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8">
-        <v>17400</v>
       </c>
     </row>
   </sheetData>
